--- a/forms/trg/Formulir_TRG_marketingbhvr.xlsx
+++ b/forms/trg/Formulir_TRG_marketingbhvr.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,19 +913,11 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Elvita Bellani, M.Sc</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Indrianty Sudirman</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
@@ -946,12 +938,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Romi Setiawan, MSM</t>
+          <t>Elvita Bellani, M.Sc</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -964,21 +956,9 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2761-4403</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdikbud.go.id/profile</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57212373818</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -991,12 +971,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Elvita Bellani, M.Sc</t>
+          <t>Romi Setiawan, MSM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,9 +989,21 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2761-4403</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/profile</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57212373818</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1024,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Romi Setiawan, MSM</t>
+          <t>Elvita Bellani, M.Sc</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1042,21 +1034,9 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2761-4403</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdikbud.go.id/profile</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>57212373818</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1069,17 +1049,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof Aghavni Grigor Hakoyban</t>
+          <t>Romi Setiawan, MSM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Armenian State University of Economics (ASUE)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1087,9 +1067,21 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2761-4403</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/profile</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57212373818</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1102,17 +1094,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mahmoud Mohamed Ahmed Abd Ellatif</t>
+          <t>Prof Aghavni Grigor Hakoyban</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University of Jeddah and AI –Helawn University - Egypt</t>
+          <t>Armenian State University of Economics (ASUE)</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1135,24 +1127,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Adel Abou Amer, PhD</t>
+          <t>Prof. Dr. Mahmoud Mohamed Ahmed Abd Ellatif</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Sains Malaysia</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Sustainable Tourism Development</t>
-        </is>
-      </c>
+          <t>University of Jeddah and AI –Helawn University - Egypt</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1172,29 +1160,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Nur Fajar Alfitra, S.Psi., M.Sc.</t>
+          <t>Adel Abou Amer, PhD</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Universiti Sains Malaysia</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Please select listing to show.</t>
+          <t>Sustainable Tourism Development</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0009-0004-7650-1183</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1209,12 +1197,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Salsyahrani Qurana R</t>
+          <t>Nur Fajar Alfitra, S.Psi., M.Sc.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1227,7 +1215,11 @@
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0004-7650-1183</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1242,12 +1234,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Faradiba Besse</t>
+          <t>Salsyahrani Qurana R</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1260,11 +1252,7 @@
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0009-0005-6620-4529</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1277,18 +1265,38 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Faradiba Besse</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The Marketing and Behavioural Research Lab is a multidisciplinary team focused on understanding the shifting dynamics of consumer behaviour, particularly in response to technological advancements and globalisation.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-6620-4529</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1477,15 +1485,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_marketingbhvr.xlsx
+++ b/forms/trg/Formulir_TRG_marketingbhvr.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Indrianty Sudirman</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
